--- a/Configs/GameConfig/Datas/关卡.xlsx
+++ b/Configs/GameConfig/Datas/关卡.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Godot\GodotProject\GodotGameFramework\Configs\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -63,6 +68,9 @@
     <t>Waves</t>
   </si>
   <si>
+    <t>pos</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -75,6 +83,9 @@
     <t>(array#sep=|),MonsterSpawnWaves</t>
   </si>
   <si>
+    <t>vector3</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -99,16 +110,25 @@
     <t>2,1|2,1|2,2|2,2|2,3|2,3|2,4|2,4</t>
   </si>
   <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
     <t>1-2</t>
   </si>
   <si>
     <t>2,1|2,1|2,2|2,2|2,3|2,3|2,4|2,5</t>
   </si>
   <si>
+    <t>1,1,2</t>
+  </si>
+  <si>
     <t>1-3</t>
   </si>
   <si>
     <t>2,1|2,1|2,2|2,2|2,3|2,3|2,4|2,6</t>
+  </si>
+  <si>
+    <t>1,1,3</t>
   </si>
 </sst>
 </file>
@@ -116,10 +136,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -627,19 +647,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1135,7 +1155,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AH15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
@@ -1167,7 +1187,9 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -1237,21 +1259,23 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:34">
       <c r="A3" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="11"/>
+        <v>9</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="13"/>
@@ -1283,7 +1307,7 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:34">
       <c r="A4" s="11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
@@ -1321,16 +1345,16 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:34">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -1368,15 +1392,17 @@
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="17"/>
+        <v>18</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="H6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="18"/>
@@ -1387,15 +1413,17 @@
         <v>2</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="17"/>
+        <v>21</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="H7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="18"/>
@@ -1406,15 +1434,17 @@
         <v>3</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="17"/>
+        <v>24</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="H8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="18"/>
